--- a/etf_holdings/2026-09-09_00990A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-09_00990A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:09</t>
+          <t>2026-09-09 00:51:17</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:09</t>
+          <t>2026-09-09 00:51:17</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:09</t>
+          <t>2026-09-09 00:51:17</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:10</t>
+          <t>2026-09-09 00:51:19</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:10</t>
+          <t>2026-09-09 00:51:19</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:10</t>
+          <t>2026-09-09 00:51:19</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:10</t>
+          <t>2026-09-09 00:51:19</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:10</t>
+          <t>2026-09-09 00:51:19</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:11</t>
+          <t>2026-09-09 00:51:20</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:11</t>
+          <t>2026-09-09 00:51:20</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:11</t>
+          <t>2026-09-09 00:51:20</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:11</t>
+          <t>2026-09-09 00:51:20</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:11</t>
+          <t>2026-09-09 00:51:20</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:11</t>
+          <t>2026-09-09 00:51:20</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:11</t>
+          <t>2026-09-09 00:51:20</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:11</t>
+          <t>2026-09-09 00:51:20</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:11</t>
+          <t>2026-09-09 00:51:20</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">

--- a/etf_holdings/2026-09-09_00990A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-09_00990A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:17</t>
+          <t>2026-09-09 01:16:49</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:17</t>
+          <t>2026-09-09 01:16:49</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:17</t>
+          <t>2026-09-09 01:16:49</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:19</t>
+          <t>2026-09-09 01:17:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:19</t>
+          <t>2026-09-09 01:17:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:19</t>
+          <t>2026-09-09 01:17:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:19</t>
+          <t>2026-09-09 01:17:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:19</t>
+          <t>2026-09-09 01:17:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:20</t>
+          <t>2026-09-09 01:17:12</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:20</t>
+          <t>2026-09-09 01:17:12</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:20</t>
+          <t>2026-09-09 01:17:12</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:20</t>
+          <t>2026-09-09 01:17:12</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:20</t>
+          <t>2026-09-09 01:17:12</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:20</t>
+          <t>2026-09-09 01:17:12</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:20</t>
+          <t>2026-09-09 01:17:12</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:20</t>
+          <t>2026-09-09 01:17:12</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:20</t>
+          <t>2026-09-09 01:17:12</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">

--- a/etf_holdings/2026-09-09_00990A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-09_00990A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:49</t>
+          <t>2026-09-09 19:33:58</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,17 +509,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-2.82%5340</t>
+          <t>+0.66%5375</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-2.82%</t>
+          <t>+0.66%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>5375</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -537,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:49</t>
+          <t>2026-09-09 19:33:58</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:49</t>
+          <t>2026-09-09 19:33:58</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -635,17 +635,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+0.41%2470</t>
+          <t>-0.2%2465</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+0.41%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2470</t>
+          <t>2465</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:00</t>
+          <t>2026-09-09 19:33:59</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -698,17 +698,17 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-1.05%4710</t>
+          <t>-1.8%4625</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-1.05%</t>
+          <t>-1.8%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4710</t>
+          <t>4625</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:00</t>
+          <t>2026-09-09 19:33:59</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -761,17 +761,17 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-2.43%1805</t>
+          <t>-0.55%1795</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-2.43%</t>
+          <t>-0.55%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1805</t>
+          <t>1795</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:00</t>
+          <t>2026-09-09 19:33:59</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -824,17 +824,17 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+0.53%954</t>
+          <t>+4.09%993</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+0.53%</t>
+          <t>+4.09%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>993</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -852,7 +852,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:00</t>
+          <t>2026-09-09 19:33:59</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:00</t>
+          <t>2026-09-09 19:33:59</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:12</t>
+          <t>2026-09-09 19:34:01</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1013,17 +1013,17 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-3.95%3285</t>
+          <t>+2.89%3380</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-3.95%</t>
+          <t>+2.89%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3285</t>
+          <t>3380</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:12</t>
+          <t>2026-09-09 19:34:01</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-1.82%1345</t>
+          <t>0%1345</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-1.82%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:12</t>
+          <t>2026-09-09 19:34:01</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1139,17 +1139,17 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+5.56%5795</t>
+          <t>-3.11%5615</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+5.56%</t>
+          <t>-3.11%</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5795</t>
+          <t>5615</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:12</t>
+          <t>2026-09-09 19:34:01</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1202,17 +1202,17 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-1.65%268.5</t>
+          <t>+0.56%270</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-1.65%</t>
+          <t>+0.56%</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>268.5</t>
+          <t>270</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:12</t>
+          <t>2026-09-09 19:34:01</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-0.48%618</t>
+          <t>+3.56%640</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-0.48%</t>
+          <t>+3.56%</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>640</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:12</t>
+          <t>2026-09-09 19:34:01</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:12</t>
+          <t>2026-09-09 19:34:01</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1391,17 +1391,17 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-6.9%1955</t>
+          <t>+3.07%2015</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-6.9%</t>
+          <t>+3.07%</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1955</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:12</t>
+          <t>2026-09-09 19:34:01</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1454,17 +1454,17 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-2.38%1025</t>
+          <t>+8.29%1110</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-2.38%</t>
+          <t>+8.29%</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1025</t>
+          <t>1110</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:12</t>
+          <t>2026-09-09 19:34:01</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1517,17 +1517,17 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-6.52%1935</t>
+          <t>+2.07%1975</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-6.52%</t>
+          <t>+2.07%</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1935</t>
+          <t>1975</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">

--- a/etf_holdings/2026-09-09_00990A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-09_00990A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:58</t>
+          <t>2026-09-09 22:37:23</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:58</t>
+          <t>2026-09-09 22:37:23</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:58</t>
+          <t>2026-09-09 22:37:23</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:59</t>
+          <t>2026-09-09 22:37:24</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:59</t>
+          <t>2026-09-09 22:37:24</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:59</t>
+          <t>2026-09-09 22:37:24</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:59</t>
+          <t>2026-09-09 22:37:24</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:59</t>
+          <t>2026-09-09 22:37:24</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:01</t>
+          <t>2026-09-09 22:37:26</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:01</t>
+          <t>2026-09-09 22:37:26</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:01</t>
+          <t>2026-09-09 22:37:26</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:01</t>
+          <t>2026-09-09 22:37:26</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:01</t>
+          <t>2026-09-09 22:37:26</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:01</t>
+          <t>2026-09-09 22:37:26</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:01</t>
+          <t>2026-09-09 22:37:26</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:01</t>
+          <t>2026-09-09 22:37:26</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:01</t>
+          <t>2026-09-09 22:37:26</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">

--- a/etf_holdings/2026-09-09_00990A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-09_00990A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:23</t>
+          <t>2026-09-09 22:49:17</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:23</t>
+          <t>2026-09-09 22:49:17</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:23</t>
+          <t>2026-09-09 22:49:17</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:24</t>
+          <t>2026-09-09 22:49:18</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:24</t>
+          <t>2026-09-09 22:49:18</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:24</t>
+          <t>2026-09-09 22:49:18</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:24</t>
+          <t>2026-09-09 22:49:18</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:24</t>
+          <t>2026-09-09 22:49:18</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:26</t>
+          <t>2026-09-09 22:49:19</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:26</t>
+          <t>2026-09-09 22:49:19</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:26</t>
+          <t>2026-09-09 22:49:19</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:26</t>
+          <t>2026-09-09 22:49:19</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:26</t>
+          <t>2026-09-09 22:49:19</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:26</t>
+          <t>2026-09-09 22:49:19</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:26</t>
+          <t>2026-09-09 22:49:19</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:26</t>
+          <t>2026-09-09 22:49:19</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:26</t>
+          <t>2026-09-09 22:49:19</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">

--- a/etf_holdings/2026-09-09_00990A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-09_00990A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:17</t>
+          <t>2026-09-09 23:10:20</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:17</t>
+          <t>2026-09-09 23:10:20</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:17</t>
+          <t>2026-09-09 23:10:20</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:18</t>
+          <t>2026-09-09 23:10:21</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:18</t>
+          <t>2026-09-09 23:10:21</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:18</t>
+          <t>2026-09-09 23:10:21</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:18</t>
+          <t>2026-09-09 23:10:21</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:18</t>
+          <t>2026-09-09 23:10:21</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:19</t>
+          <t>2026-09-09 23:10:22</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:19</t>
+          <t>2026-09-09 23:10:22</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:19</t>
+          <t>2026-09-09 23:10:22</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:19</t>
+          <t>2026-09-09 23:10:22</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:19</t>
+          <t>2026-09-09 23:10:22</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:19</t>
+          <t>2026-09-09 23:10:22</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:19</t>
+          <t>2026-09-09 23:10:22</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:19</t>
+          <t>2026-09-09 23:10:22</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:19</t>
+          <t>2026-09-09 23:10:22</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
